--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:08</t>
+    <t xml:space="preserve">2026-09-17 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:04</t>
+    <t xml:space="preserve">2026-09-23 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:33</t>
+    <t xml:space="preserve">2026-10-02 13:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:32</t>
+    <t xml:space="preserve">2026-10-05 10:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
